--- a/output/SKU_ENTRADA_ALMACEN_completado.xlsx
+++ b/output/SKU_ENTRADA_ALMACEN_completado.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="ENTRADA LIMPIA" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Hoja1" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="R2 VALIDADO QUANTS" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +443,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SUMMER COOL 2.0 SERENITY</t>
+          <t>R2 SPORT 5"</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -457,7 +458,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SUMMER COOL 2.0 SERENITY</t>
+          <t>R2 RUNNING 3,5"</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -472,7 +473,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SUMMER COOL 2.0 SERENITY</t>
+          <t>R2 SPORT 5"</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -517,7 +518,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SUMMER COOL 2.0 SERENITY</t>
+          <t>R2 SPORT 5"</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -547,7 +548,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SUMMER COOL 2.0 SERENITY</t>
+          <t>R2 SPORT 5"</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -562,7 +563,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SUMMER COOL 2.0 SERENITY</t>
+          <t>R2 SPORT 5"</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -697,7 +698,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SUMMER COOL 2.0 SERENITY</t>
+          <t>R2 SPORT 5"</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -742,7 +743,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SUMMER COOL 2.0 SERENITY</t>
+          <t>R2 RUNNING 3,5"</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -802,7 +803,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SUMMER COOL 2.0 SERENITY</t>
+          <t>R2 RUNNING 3,5"</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -892,7 +893,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>SUMMER COOL 2.0 SERENITY</t>
+          <t>R2 SPORT 5"</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -982,7 +983,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>SUMMER COOL 2.0 SERENITY</t>
+          <t>R2 RUNNING 3,5"</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -1267,7 +1268,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>SUMMER COOL 2.0 SERENITY</t>
+          <t>R2 RUNNING 3,5"</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -1357,7 +1358,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>SUMMER COOL 2.0 SERENITY</t>
+          <t>R2 SPORT 5"</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -2017,7 +2018,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>SUMMER COOL 2.0 SERENITY</t>
+          <t>R2 RUNNING 3,5"</t>
         </is>
       </c>
       <c r="C107" t="n">
@@ -2032,7 +2033,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>SUMMER COOL 2.0 SERENITY</t>
+          <t>R2 RUNNING 3,5"</t>
         </is>
       </c>
       <c r="C108" t="n">
@@ -2047,7 +2048,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>SUMMER COOL 2.0 SERENITY</t>
+          <t>R2 RUNNING 3,5"</t>
         </is>
       </c>
       <c r="C109" t="n">
@@ -2062,7 +2063,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>SUMMER COOL 2.0 SERENITY</t>
+          <t>R2 RUNNING 3,5"</t>
         </is>
       </c>
       <c r="C110" t="n">
@@ -3340,7 +3341,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F194"/>
+  <dimension ref="A1:G194"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3361,15 +3362,20 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>PRODUCTO_ODOO</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>SKU_CATALOGO</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>FUENTE</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>ESTADO</t>
         </is>
@@ -3383,7 +3389,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SUMMER COOL 2.0 SERENITY</t>
+          <t>R2 SPORT 5"</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -3391,17 +3397,22 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>SERVIDA43TL</t>
+          <t>R2 SPORT  5" (Negro, L)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>alias_servida; global:MANUFACTURADO</t>
+          <t>SSR2VIU43TL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>ok_sku_corregido</t>
+          <t>quants:Quants__stock.quant___1__5059.xlsx</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>ok_quants_odoo</t>
         </is>
       </c>
     </row>
@@ -3413,7 +3424,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SUMMER COOL 2.0 SERENITY</t>
+          <t>R2 RUNNING 3,5"</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -3421,17 +3432,22 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>SERVIDA12TS</t>
+          <t>R2 RUNNING 3,5" (Azul Rey, S)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>color_13_to_12; global:MANUFACTURADO</t>
+          <t>SRR2VIU13TS</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ok_sku_corregido</t>
+          <t>quants:Quants__stock.quant___2__3ab0.xlsx</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>ok_quants_odoo</t>
         </is>
       </c>
     </row>
@@ -3443,7 +3459,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SUMMER COOL 2.0 SERENITY</t>
+          <t>R2 SPORT 5"</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -3451,17 +3467,22 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>SERVIDA66TXL</t>
+          <t>R2 SPORT  5" (Verde Militar, XL)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>alias_servida; global:MANUFACTURADO</t>
+          <t>SSR2VIU66TXL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ok_sku_corregido</t>
+          <t>quants:Quants__stock.quant___1__5059.xlsx</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>ok_quants_odoo</t>
         </is>
       </c>
     </row>
@@ -3479,17 +3500,18 @@
       <c r="C5" t="n">
         <v>39</v>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
         <is>
           <t>BACCCDA158TL</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -3509,17 +3531,18 @@
       <c r="C6" t="n">
         <v>37</v>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
         <is>
           <t>DAYCSTDA66TM</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -3533,7 +3556,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SUMMER COOL 2.0 SERENITY</t>
+          <t>R2 SPORT 5"</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -3541,17 +3564,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>SERVIDA66TL</t>
+          <t>R2 SPORT  5" (Verde Militar, L)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>alias_servida; global:MANUFACTURADO</t>
+          <t>SSR2VIU66TL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ok_sku_corregido</t>
+          <t>quants:Quants__stock.quant___1__5059.xlsx</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>ok_quants_odoo</t>
         </is>
       </c>
     </row>
@@ -3569,17 +3597,18 @@
       <c r="C8" t="n">
         <v>34</v>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
         <is>
           <t>DAYCSTDA66TS</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -3593,7 +3622,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SUMMER COOL 2.0 SERENITY</t>
+          <t>R2 SPORT 5"</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -3601,17 +3630,22 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>SERVIDA43TS</t>
+          <t>R2 SPORT  5" (Negro, S)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>alias_servida; global:MANUFACTURADO</t>
+          <t>SSR2VIU43TS</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ok_sku_corregido</t>
+          <t>quants:Quants__stock.quant___1__5059.xlsx</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>ok_quants_odoo</t>
         </is>
       </c>
     </row>
@@ -3623,7 +3657,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SUMMER COOL 2.0 SERENITY</t>
+          <t>R2 SPORT 5"</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -3631,17 +3665,22 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>SERVIDA70TM</t>
+          <t>R2 SPORT  5" (Vinotinto, M)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>alias_servida; global:MANUFACTURADO</t>
+          <t>SSR2VIU70TM</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ok_sku_corregido</t>
+          <t>quants:Quants__stock.quant___1__5059.xlsx</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>ok_quants_odoo</t>
         </is>
       </c>
     </row>
@@ -3659,17 +3698,18 @@
       <c r="C11" t="n">
         <v>31</v>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
         <is>
           <t>DAYCSTDA66TXL</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -3689,17 +3729,18 @@
       <c r="C12" t="n">
         <v>30</v>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
         <is>
           <t>DAYCSTCA43TS</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -3719,17 +3760,18 @@
       <c r="C13" t="n">
         <v>29</v>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
         <is>
           <t>SHUNTCA43TXL</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -3749,17 +3791,18 @@
       <c r="C14" t="n">
         <v>28</v>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
         <is>
           <t>DAYCSTDA66TXS</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -3779,17 +3822,18 @@
       <c r="C15" t="n">
         <v>27</v>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
         <is>
           <t>BACCCDA38TM</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -3809,17 +3853,18 @@
       <c r="C16" t="n">
         <v>27</v>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
         <is>
           <t>BACCCDA43TXS</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -3839,17 +3884,18 @@
       <c r="C17" t="n">
         <v>24</v>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
         <is>
           <t>MARMIKI16T10</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F17" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -3869,17 +3915,18 @@
       <c r="C18" t="n">
         <v>23</v>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
         <is>
           <t>SHONTCA43TM</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -3893,7 +3940,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SUMMER COOL 2.0 SERENITY</t>
+          <t>R2 SPORT 5"</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -3901,17 +3948,22 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>SERVIDA66TM</t>
+          <t>R2 SPORT  5" (Verde Militar, M)</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>alias_servida; global:MANUFACTURADO</t>
+          <t>SSR2VIU66TM</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>ok_sku_corregido</t>
+          <t>quants:Quants__stock.quant___1__5059.xlsx</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>ok_quants_odoo</t>
         </is>
       </c>
     </row>
@@ -3929,17 +3981,18 @@
       <c r="C20" t="n">
         <v>21</v>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
         <is>
           <t>RIOMICA30TS</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F20" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -3959,17 +4012,18 @@
       <c r="C21" t="n">
         <v>21</v>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
         <is>
           <t>SARSPDA43TXS</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F21" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -3983,7 +4037,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SUMMER COOL 2.0 SERENITY</t>
+          <t>R2 RUNNING 3,5"</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -3991,17 +4045,22 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>SERVIDA43TS</t>
+          <t>R2 RUNNING 3,5" (Negro, S)</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>alias_servida; global:MANUFACTURADO</t>
+          <t>SRR2VIU43TS</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>ok_sku_corregido</t>
+          <t>ok_r2_inferred</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>ok_r2_inferred</t>
         </is>
       </c>
     </row>
@@ -4019,17 +4078,18 @@
       <c r="C23" t="n">
         <v>20</v>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
         <is>
           <t>BACCCDA158TXL</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F23" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -4049,17 +4109,18 @@
       <c r="C24" t="n">
         <v>20</v>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
         <is>
           <t>RIOMIDA48TM</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F24" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -4079,17 +4140,18 @@
       <c r="C25" t="n">
         <v>20</v>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
         <is>
           <t>SHOSUCA154TXL</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F25" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -4103,7 +4165,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SUMMER COOL 2.0 SERENITY</t>
+          <t>R2 RUNNING 3,5"</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -4111,17 +4173,22 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>SERVIDA12TS</t>
+          <t>R2 RUNNING 3,5" (Azul Marino, S)</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>color_123_to_12; global:MANUFACTURADO</t>
+          <t>SRR2VIU123TS</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>ok_sku_corregido</t>
+          <t>ok_r2_inferred</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>ok_r2_inferred</t>
         </is>
       </c>
     </row>
@@ -4139,17 +4206,18 @@
       <c r="C27" t="n">
         <v>19</v>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
         <is>
           <t>BACCCDA43TM</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F27" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -4169,17 +4237,18 @@
       <c r="C28" t="n">
         <v>19</v>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
         <is>
           <t>RIOMICA11TL</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F28" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -4199,17 +4268,18 @@
       <c r="C29" t="n">
         <v>19</v>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
         <is>
           <t>RIOMICA30TL</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F29" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -4229,17 +4299,18 @@
       <c r="C30" t="n">
         <v>19</v>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
         <is>
           <t>SHONTCA33TL</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F30" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -4259,17 +4330,18 @@
       <c r="C31" t="n">
         <v>19</v>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
         <is>
           <t>SHONTCA33TM</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F31" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -4283,7 +4355,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>SUMMER COOL 2.0 SERENITY</t>
+          <t>R2 SPORT 5"</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -4291,17 +4363,22 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>SERVIDA43TXL</t>
+          <t>R2 SPORT  5" (Negro, XL)</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>alias_servida; global:MANUFACTURADO</t>
+          <t>SSR2VIU43TXL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>ok_sku_corregido</t>
+          <t>quants:Quants__stock.quant___1__5059.xlsx</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>ok_quants_odoo</t>
         </is>
       </c>
     </row>
@@ -4319,17 +4396,18 @@
       <c r="C33" t="n">
         <v>16</v>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
         <is>
           <t>DAYCSTDA66TL</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F33" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -4349,17 +4427,18 @@
       <c r="C34" t="n">
         <v>15</v>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
         <is>
           <t>SHONTCA66TM</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F34" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -4379,17 +4458,18 @@
       <c r="C35" t="n">
         <v>15</v>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
         <is>
           <t>SHOSUCA154TS</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F35" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -4409,17 +4489,18 @@
       <c r="C36" t="n">
         <v>15</v>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
         <is>
           <t>SHOSUCA155TXL</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F36" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -4439,17 +4520,18 @@
       <c r="C37" t="n">
         <v>13</v>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
         <is>
           <t>SHONTCA66TL</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F37" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -4463,7 +4545,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>SUMMER COOL 2.0 SERENITY</t>
+          <t>R2 RUNNING 3,5"</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -4471,17 +4553,22 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>SERVIDA12TM</t>
+          <t>R2 RUNNING 3,5" (Azul Marino, M)</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>color_123_to_12; global:MANUFACTURADO</t>
+          <t>SRR2VIU123TM</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>ok_sku_corregido</t>
+          <t>ok_r2_inferred</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>ok_r2_inferred</t>
         </is>
       </c>
     </row>
@@ -4499,17 +4586,18 @@
       <c r="C39" t="n">
         <v>12</v>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
         <is>
           <t>LARIMJDA12TL</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F39" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -4529,17 +4617,18 @@
       <c r="C40" t="n">
         <v>12</v>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
         <is>
           <t>LARIMJDA12TXL</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F40" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -4559,17 +4648,18 @@
       <c r="C41" t="n">
         <v>11</v>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
         <is>
           <t>LARIMJDA12TXS</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F41" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -4589,17 +4679,18 @@
       <c r="C42" t="n">
         <v>11</v>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
         <is>
           <t>SHONTCA43TXL</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F42" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -4619,17 +4710,18 @@
       <c r="C43" t="n">
         <v>11</v>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
         <is>
           <t>SHONTCA66TS</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F43" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -4649,17 +4741,18 @@
       <c r="C44" t="n">
         <v>10</v>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
         <is>
           <t>RIOMIDA66TL</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F44" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -4679,17 +4772,18 @@
       <c r="C45" t="n">
         <v>10</v>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
         <is>
           <t>SHONTCA33TS</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F45" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -4709,17 +4803,18 @@
       <c r="C46" t="n">
         <v>10</v>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
         <is>
           <t>SHONTCA33TXL</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F46" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -4739,17 +4834,18 @@
       <c r="C47" t="n">
         <v>10</v>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
         <is>
           <t>SHOSUKI155T1</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F47" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -4769,17 +4865,18 @@
       <c r="C48" t="n">
         <v>10</v>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
         <is>
           <t>SHOSUKI155T10</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F48" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -4799,17 +4896,18 @@
       <c r="C49" t="n">
         <v>9</v>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
         <is>
           <t>SARSPKI43T10</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F49" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -4829,17 +4927,18 @@
       <c r="C50" t="n">
         <v>9</v>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
         <is>
           <t>SHOSUKI154T12</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F50" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -4859,17 +4958,18 @@
       <c r="C51" t="n">
         <v>9</v>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
         <is>
           <t>SHOSUKI155T12</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F51" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -4889,17 +4989,18 @@
       <c r="C52" t="n">
         <v>9</v>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
         <is>
           <t>SHOSUKI155T6</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F52" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -4919,17 +5020,18 @@
       <c r="C53" t="n">
         <v>9</v>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
         <is>
           <t>SHOSUKI155T8</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F53" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -4949,17 +5051,18 @@
       <c r="C54" t="n">
         <v>8</v>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
         <is>
           <t>SHONTCA43TL</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F54" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -4979,17 +5082,18 @@
       <c r="C55" t="n">
         <v>8</v>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
         <is>
           <t>SHOSUKI154T6</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F55" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -5009,17 +5113,18 @@
       <c r="C56" t="n">
         <v>8</v>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
         <is>
           <t>SHOSUKI154T8</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F56" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -5033,7 +5138,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>SUMMER COOL 2.0 SERENITY</t>
+          <t>R2 RUNNING 3,5"</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -5041,17 +5146,22 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>SERVIDA12TL</t>
+          <t>R2 RUNNING 3,5" (Azul Marino, L)</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>color_123_to_12; global:MANUFACTURADO</t>
+          <t>SRR2VIU123TL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>ok_sku_corregido</t>
+          <t>ok_r2_inferred</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>ok_r2_inferred</t>
         </is>
       </c>
     </row>
@@ -5069,17 +5179,18 @@
       <c r="C58" t="n">
         <v>7</v>
       </c>
-      <c r="D58" t="inlineStr">
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
         <is>
           <t>SHONTCA31TL</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F58" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -5099,17 +5210,18 @@
       <c r="C59" t="n">
         <v>7</v>
       </c>
-      <c r="D59" t="inlineStr">
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
         <is>
           <t>SHONTCA66TXL</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F59" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -5129,17 +5241,18 @@
       <c r="C60" t="n">
         <v>7</v>
       </c>
-      <c r="D60" t="inlineStr">
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
         <is>
           <t>SHOSUKI154T1</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F60" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -5159,17 +5272,18 @@
       <c r="C61" t="n">
         <v>7</v>
       </c>
-      <c r="D61" t="inlineStr">
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
         <is>
           <t>SHOSUKI154T14</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F61" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -5189,17 +5303,18 @@
       <c r="C62" t="n">
         <v>7</v>
       </c>
-      <c r="D62" t="inlineStr">
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
         <is>
           <t>SHOSUKI155T4</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F62" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -5213,7 +5328,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>SUMMER COOL 2.0 SERENITY</t>
+          <t>R2 SPORT 5"</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -5221,17 +5336,22 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>SERVIDA43TM</t>
+          <t>R2 SPORT  5" (Negro, M)</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>alias_servida; global:MANUFACTURADO</t>
+          <t>SSR2VIU43TM</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>ok_sku_corregido</t>
+          <t>quants:Quants__stock.quant___1__5059.xlsx</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>ok_quants_odoo</t>
         </is>
       </c>
     </row>
@@ -5249,17 +5369,18 @@
       <c r="C64" t="n">
         <v>6</v>
       </c>
-      <c r="D64" t="inlineStr">
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
         <is>
           <t>DOMBFCA30TS</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F64" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -5279,17 +5400,18 @@
       <c r="C65" t="n">
         <v>6</v>
       </c>
-      <c r="D65" t="inlineStr">
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr">
         <is>
           <t>SHONTCA30TM</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F65" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -5309,17 +5431,18 @@
       <c r="C66" t="n">
         <v>6</v>
       </c>
-      <c r="D66" t="inlineStr">
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
         <is>
           <t>SHONTCA31TM</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F66" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -5339,17 +5462,18 @@
       <c r="C67" t="n">
         <v>6</v>
       </c>
-      <c r="D67" t="inlineStr">
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
         <is>
           <t>SHOSUKI154T10</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F67" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -5369,17 +5493,18 @@
       <c r="C68" t="n">
         <v>6</v>
       </c>
-      <c r="D68" t="inlineStr">
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
         <is>
           <t>SHOSUKI154T2</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F68" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -5399,17 +5524,18 @@
       <c r="C69" t="n">
         <v>6</v>
       </c>
-      <c r="D69" t="inlineStr">
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
         <is>
           <t>SHOSUKI155T2</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F69" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -5429,17 +5555,18 @@
       <c r="C70" t="n">
         <v>5</v>
       </c>
-      <c r="D70" t="inlineStr">
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
         <is>
           <t>SHOSUCA154TM</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F70" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -5459,17 +5586,18 @@
       <c r="C71" t="n">
         <v>5</v>
       </c>
-      <c r="D71" t="inlineStr">
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
         <is>
           <t>SHOSUCA155T2XL</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F71" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -5489,17 +5617,18 @@
       <c r="C72" t="n">
         <v>5</v>
       </c>
-      <c r="D72" t="inlineStr">
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
         <is>
           <t>SHOSUKI156T14</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F72" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -5519,17 +5648,18 @@
       <c r="C73" t="n">
         <v>5</v>
       </c>
-      <c r="D73" t="inlineStr">
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
         <is>
           <t>SHOSUKI156T8</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F73" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -5549,17 +5679,18 @@
       <c r="C74" t="n">
         <v>4</v>
       </c>
-      <c r="D74" t="inlineStr">
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
         <is>
           <t>MARMIKI43T12</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F74" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -5579,17 +5710,18 @@
       <c r="C75" t="n">
         <v>4</v>
       </c>
-      <c r="D75" t="inlineStr">
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr">
         <is>
           <t>SHONTCA30TL</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F75" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -5609,17 +5741,18 @@
       <c r="C76" t="n">
         <v>4</v>
       </c>
-      <c r="D76" t="inlineStr">
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
         <is>
           <t>SHONTCA31TS</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F76" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -5639,17 +5772,18 @@
       <c r="C77" t="n">
         <v>4</v>
       </c>
-      <c r="D77" t="inlineStr">
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr">
         <is>
           <t>SHONTCA43TS</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F77" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -5669,17 +5803,18 @@
       <c r="C78" t="n">
         <v>3</v>
       </c>
-      <c r="D78" t="inlineStr">
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr">
         <is>
           <t>BAOCCCA158TM</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F78" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -5699,17 +5834,18 @@
       <c r="C79" t="n">
         <v>3</v>
       </c>
-      <c r="D79" t="inlineStr">
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr">
         <is>
           <t>BAOCCCA158TXS</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F79" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -5729,17 +5865,18 @@
       <c r="C80" t="n">
         <v>3</v>
       </c>
-      <c r="D80" t="inlineStr">
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr">
         <is>
           <t>LMOFIDA09TXL</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F80" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -5759,19 +5896,20 @@
       <c r="C81" t="n">
         <v>3</v>
       </c>
-      <c r="D81" t="inlineStr">
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr">
         <is>
           <t>MILMIDA66TS</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>alias_mila; global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>ok_sku_corregido</t>
+          <t>ok_catalog:alias_mila; global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>ok_catalog:alias_mila</t>
         </is>
       </c>
     </row>
@@ -5789,17 +5927,18 @@
       <c r="C82" t="n">
         <v>3</v>
       </c>
-      <c r="D82" t="inlineStr">
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr">
         <is>
           <t>SHOSUCA154TL</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F82" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -5819,17 +5958,18 @@
       <c r="C83" t="n">
         <v>3</v>
       </c>
-      <c r="D83" t="inlineStr">
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr">
         <is>
           <t>SHOSUKI154T4</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F83" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -5849,17 +5989,18 @@
       <c r="C84" t="n">
         <v>3</v>
       </c>
-      <c r="D84" t="inlineStr">
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr">
         <is>
           <t>SHOSUKI156T10</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F84" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -5879,17 +6020,18 @@
       <c r="C85" t="n">
         <v>2</v>
       </c>
-      <c r="D85" t="inlineStr">
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr">
         <is>
           <t>CLAMICA16TXL</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F85" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -5909,17 +6051,18 @@
       <c r="C86" t="n">
         <v>2</v>
       </c>
-      <c r="D86" t="inlineStr">
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr">
         <is>
           <t>CLAMICA43TS</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F86" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -5939,17 +6082,18 @@
       <c r="C87" t="n">
         <v>2</v>
       </c>
-      <c r="D87" t="inlineStr">
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr">
         <is>
           <t>DAYCSTCA66TS</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F87" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -5969,17 +6113,18 @@
       <c r="C88" t="n">
         <v>2</v>
       </c>
-      <c r="D88" t="inlineStr">
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr">
         <is>
           <t>GEMBADA12TS</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F88" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -5999,17 +6144,18 @@
       <c r="C89" t="n">
         <v>2</v>
       </c>
-      <c r="D89" t="inlineStr">
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr">
         <is>
           <t>GEOMACADA03TXS</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F89" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -6029,17 +6175,18 @@
       <c r="C90" t="n">
         <v>2</v>
       </c>
-      <c r="D90" t="inlineStr">
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr">
         <is>
           <t>LMOFIDA09TXS</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F90" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -6059,17 +6206,18 @@
       <c r="C91" t="n">
         <v>2</v>
       </c>
-      <c r="D91" t="inlineStr">
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" t="inlineStr">
         <is>
           <t>MARMICA30TL</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F91" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -6089,17 +6237,18 @@
       <c r="C92" t="n">
         <v>2</v>
       </c>
-      <c r="D92" t="inlineStr">
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" t="inlineStr">
         <is>
           <t>MARMICA43TS</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F92" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -6119,17 +6268,18 @@
       <c r="C93" t="n">
         <v>2</v>
       </c>
-      <c r="D93" t="inlineStr">
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="inlineStr">
         <is>
           <t>MARMIDA16TM</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F93" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -6149,17 +6299,18 @@
       <c r="C94" t="n">
         <v>2</v>
       </c>
-      <c r="D94" t="inlineStr">
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" t="inlineStr">
         <is>
           <t>MARMIKI53T8</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F94" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -6179,17 +6330,18 @@
       <c r="C95" t="n">
         <v>2</v>
       </c>
-      <c r="D95" t="inlineStr">
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="inlineStr">
         <is>
           <t>MAYFNDA16TM</t>
         </is>
       </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F95" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -6209,17 +6361,18 @@
       <c r="C96" t="n">
         <v>2</v>
       </c>
-      <c r="D96" t="inlineStr">
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="inlineStr">
         <is>
           <t>MIKFNDA13TXL</t>
         </is>
       </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F96" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -6239,17 +6392,18 @@
       <c r="C97" t="n">
         <v>2</v>
       </c>
-      <c r="D97" t="inlineStr">
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" t="inlineStr">
         <is>
           <t>SARSPKI13T4</t>
         </is>
       </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F97" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -6269,17 +6423,18 @@
       <c r="C98" t="n">
         <v>2</v>
       </c>
-      <c r="D98" t="inlineStr">
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" t="inlineStr">
         <is>
           <t>SHONTCA31TXL</t>
         </is>
       </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F98" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -6299,17 +6454,18 @@
       <c r="C99" t="n">
         <v>2</v>
       </c>
-      <c r="D99" t="inlineStr">
+      <c r="D99" t="inlineStr"/>
+      <c r="E99" t="inlineStr">
         <is>
           <t>SHONTDA31TM</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F99" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -6329,17 +6485,18 @@
       <c r="C100" t="n">
         <v>2</v>
       </c>
-      <c r="D100" t="inlineStr">
+      <c r="D100" t="inlineStr"/>
+      <c r="E100" t="inlineStr">
         <is>
           <t>SHOSUCA153TL</t>
         </is>
       </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F100" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -6359,17 +6516,18 @@
       <c r="C101" t="n">
         <v>2</v>
       </c>
-      <c r="D101" t="inlineStr">
+      <c r="D101" t="inlineStr"/>
+      <c r="E101" t="inlineStr">
         <is>
           <t>SHOSUKI153T12</t>
         </is>
       </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F101" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -6389,17 +6547,18 @@
       <c r="C102" t="n">
         <v>2</v>
       </c>
-      <c r="D102" t="inlineStr">
+      <c r="D102" t="inlineStr"/>
+      <c r="E102" t="inlineStr">
         <is>
           <t>SHOSUKI153T14</t>
         </is>
       </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F102" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -6419,17 +6578,18 @@
       <c r="C103" t="n">
         <v>2</v>
       </c>
-      <c r="D103" t="inlineStr">
+      <c r="D103" t="inlineStr"/>
+      <c r="E103" t="inlineStr">
         <is>
           <t>SHOSUKI153T8</t>
         </is>
       </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F103" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -6449,17 +6609,18 @@
       <c r="C104" t="n">
         <v>2</v>
       </c>
-      <c r="D104" t="inlineStr">
+      <c r="D104" t="inlineStr"/>
+      <c r="E104" t="inlineStr">
         <is>
           <t>SHOSUKI156T12</t>
         </is>
       </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F104" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -6479,17 +6640,18 @@
       <c r="C105" t="n">
         <v>2</v>
       </c>
-      <c r="D105" t="inlineStr">
+      <c r="D105" t="inlineStr"/>
+      <c r="E105" t="inlineStr">
         <is>
           <t>SHOSUKI156T2</t>
         </is>
       </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F105" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -6509,17 +6671,18 @@
       <c r="C106" t="n">
         <v>2</v>
       </c>
-      <c r="D106" t="inlineStr">
+      <c r="D106" t="inlineStr"/>
+      <c r="E106" t="inlineStr">
         <is>
           <t>SHUNTDA43TXS</t>
         </is>
       </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F106" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -6533,7 +6696,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>SUMMER COOL 2.0 SERENITY</t>
+          <t>R2 RUNNING 3,5"</t>
         </is>
       </c>
       <c r="C107" t="n">
@@ -6541,17 +6704,22 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>SERVIDA12TXS</t>
+          <t>R2 RUNNING 3,5" (Azul Marino, XS)</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>color_123_to_12; global:MANUFACTURADO</t>
+          <t>SRR2VIU123TXS</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>ok_sku_corregido</t>
+          <t>ok_r2_inferred</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>ok_r2_inferred</t>
         </is>
       </c>
     </row>
@@ -6563,7 +6731,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>SUMMER COOL 2.0 SERENITY</t>
+          <t>R2 RUNNING 3,5"</t>
         </is>
       </c>
       <c r="C108" t="n">
@@ -6571,17 +6739,22 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>SERVIDA43TL</t>
+          <t>R2 RUNNING 3,5" (Negro, L)</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>alias_servida; global:MANUFACTURADO</t>
+          <t>SRR2VIU43TL</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>ok_sku_corregido</t>
+          <t>ok_r2_inferred</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>ok_r2_inferred</t>
         </is>
       </c>
     </row>
@@ -6593,7 +6766,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>SUMMER COOL 2.0 SERENITY</t>
+          <t>R2 RUNNING 3,5"</t>
         </is>
       </c>
       <c r="C109" t="n">
@@ -6601,17 +6774,22 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>SERVIDA43TM</t>
+          <t>R2 RUNNING 3,5" (Negro, M)</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>alias_servida; global:MANUFACTURADO</t>
+          <t>SRR2VIU43TM</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>ok_sku_corregido</t>
+          <t>ok_r2_inferred</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>ok_r2_inferred</t>
         </is>
       </c>
     </row>
@@ -6623,7 +6801,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>SUMMER COOL 2.0 SERENITY</t>
+          <t>R2 RUNNING 3,5"</t>
         </is>
       </c>
       <c r="C110" t="n">
@@ -6631,17 +6809,22 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>SERVIDA43TXS</t>
+          <t>R2 RUNNING 3,5" (Negro, XS)</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>alias_servida; global:MANUFACTURADO</t>
+          <t>SRR2VIU43TXS</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>ok_sku_corregido</t>
+          <t>ok_r2_inferred</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>ok_r2_inferred</t>
         </is>
       </c>
     </row>
@@ -6659,17 +6842,18 @@
       <c r="C111" t="n">
         <v>1</v>
       </c>
-      <c r="D111" t="inlineStr">
+      <c r="D111" t="inlineStr"/>
+      <c r="E111" t="inlineStr">
         <is>
           <t>ADUMMCA11TS</t>
         </is>
       </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F111" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -6689,17 +6873,18 @@
       <c r="C112" t="n">
         <v>1</v>
       </c>
-      <c r="D112" t="inlineStr">
+      <c r="D112" t="inlineStr"/>
+      <c r="E112" t="inlineStr">
         <is>
           <t>ADUMMCA16TS</t>
         </is>
       </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F112" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -6719,17 +6904,18 @@
       <c r="C113" t="n">
         <v>1</v>
       </c>
-      <c r="D113" t="inlineStr">
+      <c r="D113" t="inlineStr"/>
+      <c r="E113" t="inlineStr">
         <is>
           <t>BACCCDA38TL</t>
         </is>
       </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F113" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -6749,17 +6935,18 @@
       <c r="C114" t="n">
         <v>1</v>
       </c>
-      <c r="D114" t="inlineStr">
+      <c r="D114" t="inlineStr"/>
+      <c r="E114" t="inlineStr">
         <is>
           <t>BACCCDA38TXS</t>
         </is>
       </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F114" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -6779,17 +6966,18 @@
       <c r="C115" t="n">
         <v>1</v>
       </c>
-      <c r="D115" t="inlineStr">
+      <c r="D115" t="inlineStr"/>
+      <c r="E115" t="inlineStr">
         <is>
           <t>BAOCCCA43TL</t>
         </is>
       </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F115" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -6809,17 +6997,18 @@
       <c r="C116" t="n">
         <v>1</v>
       </c>
-      <c r="D116" t="inlineStr">
+      <c r="D116" t="inlineStr"/>
+      <c r="E116" t="inlineStr">
         <is>
           <t>BAOCCCA43TS</t>
         </is>
       </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F116" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -6839,17 +7028,18 @@
       <c r="C117" t="n">
         <v>1</v>
       </c>
-      <c r="D117" t="inlineStr">
+      <c r="D117" t="inlineStr"/>
+      <c r="E117" t="inlineStr">
         <is>
           <t>BAOCCCA43TXL</t>
         </is>
       </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F117" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -6869,17 +7059,18 @@
       <c r="C118" t="n">
         <v>1</v>
       </c>
-      <c r="D118" t="inlineStr">
+      <c r="D118" t="inlineStr"/>
+      <c r="E118" t="inlineStr">
         <is>
           <t>BLCTCCKI210T14</t>
         </is>
       </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F118" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -6899,17 +7090,18 @@
       <c r="C119" t="n">
         <v>1</v>
       </c>
-      <c r="D119" t="inlineStr">
+      <c r="D119" t="inlineStr"/>
+      <c r="E119" t="inlineStr">
         <is>
           <t>CLADFCA70TL</t>
         </is>
       </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F119" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -6929,17 +7121,18 @@
       <c r="C120" t="n">
         <v>1</v>
       </c>
-      <c r="D120" t="inlineStr">
+      <c r="D120" t="inlineStr"/>
+      <c r="E120" t="inlineStr">
         <is>
           <t>CLAMECA12TM</t>
         </is>
       </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F120" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -6959,17 +7152,18 @@
       <c r="C121" t="n">
         <v>1</v>
       </c>
-      <c r="D121" t="inlineStr">
+      <c r="D121" t="inlineStr"/>
+      <c r="E121" t="inlineStr">
         <is>
           <t>CLAMECA16T2XL</t>
         </is>
       </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F121" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -6989,17 +7183,18 @@
       <c r="C122" t="n">
         <v>1</v>
       </c>
-      <c r="D122" t="inlineStr">
+      <c r="D122" t="inlineStr"/>
+      <c r="E122" t="inlineStr">
         <is>
           <t>CLAMICA12TM</t>
         </is>
       </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F122" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -7019,17 +7214,18 @@
       <c r="C123" t="n">
         <v>1</v>
       </c>
-      <c r="D123" t="inlineStr">
+      <c r="D123" t="inlineStr"/>
+      <c r="E123" t="inlineStr">
         <is>
           <t>CLAMICA12TS</t>
         </is>
       </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F123" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -7049,17 +7245,18 @@
       <c r="C124" t="n">
         <v>1</v>
       </c>
-      <c r="D124" t="inlineStr">
+      <c r="D124" t="inlineStr"/>
+      <c r="E124" t="inlineStr">
         <is>
           <t>CLAMICA12TXL</t>
         </is>
       </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F124" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -7079,17 +7276,18 @@
       <c r="C125" t="n">
         <v>1</v>
       </c>
-      <c r="D125" t="inlineStr">
+      <c r="D125" t="inlineStr"/>
+      <c r="E125" t="inlineStr">
         <is>
           <t>CLAMICA16TL</t>
         </is>
       </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F125" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -7109,17 +7307,18 @@
       <c r="C126" t="n">
         <v>1</v>
       </c>
-      <c r="D126" t="inlineStr">
+      <c r="D126" t="inlineStr"/>
+      <c r="E126" t="inlineStr">
         <is>
           <t>CLAMIDA12TM</t>
         </is>
       </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F126" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -7139,17 +7338,18 @@
       <c r="C127" t="n">
         <v>1</v>
       </c>
-      <c r="D127" t="inlineStr">
+      <c r="D127" t="inlineStr"/>
+      <c r="E127" t="inlineStr">
         <is>
           <t>CLAMIDA66TS</t>
         </is>
       </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F127" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -7169,17 +7369,18 @@
       <c r="C128" t="n">
         <v>1</v>
       </c>
-      <c r="D128" t="inlineStr">
+      <c r="D128" t="inlineStr"/>
+      <c r="E128" t="inlineStr">
         <is>
           <t>GEOMACADA03TL</t>
         </is>
       </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F128" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -7199,17 +7400,18 @@
       <c r="C129" t="n">
         <v>1</v>
       </c>
-      <c r="D129" t="inlineStr">
+      <c r="D129" t="inlineStr"/>
+      <c r="E129" t="inlineStr">
         <is>
           <t>GEOMACADA03TM</t>
         </is>
       </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F129" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -7229,17 +7431,18 @@
       <c r="C130" t="n">
         <v>1</v>
       </c>
-      <c r="D130" t="inlineStr">
+      <c r="D130" t="inlineStr"/>
+      <c r="E130" t="inlineStr">
         <is>
           <t>GEOMACADA03TS</t>
         </is>
       </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F130" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -7259,17 +7462,18 @@
       <c r="C131" t="n">
         <v>1</v>
       </c>
-      <c r="D131" t="inlineStr">
+      <c r="D131" t="inlineStr"/>
+      <c r="E131" t="inlineStr">
         <is>
           <t>GEOMACADA03TXL</t>
         </is>
       </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F131" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -7289,17 +7493,18 @@
       <c r="C132" t="n">
         <v>1</v>
       </c>
-      <c r="D132" t="inlineStr">
+      <c r="D132" t="inlineStr"/>
+      <c r="E132" t="inlineStr">
         <is>
           <t>HELBFDA30TS</t>
         </is>
       </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F132" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -7319,17 +7524,18 @@
       <c r="C133" t="n">
         <v>1</v>
       </c>
-      <c r="D133" t="inlineStr">
+      <c r="D133" t="inlineStr"/>
+      <c r="E133" t="inlineStr">
         <is>
           <t>HELBFDA30TXL</t>
         </is>
       </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F133" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -7349,17 +7555,18 @@
       <c r="C134" t="n">
         <v>1</v>
       </c>
-      <c r="D134" t="inlineStr">
+      <c r="D134" t="inlineStr"/>
+      <c r="E134" t="inlineStr">
         <is>
           <t>HELBFDA43TXS</t>
         </is>
       </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F134" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -7379,17 +7586,18 @@
       <c r="C135" t="n">
         <v>1</v>
       </c>
-      <c r="D135" t="inlineStr">
+      <c r="D135" t="inlineStr"/>
+      <c r="E135" t="inlineStr">
         <is>
           <t>LARIMJDA16TS</t>
         </is>
       </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F135" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -7409,17 +7617,18 @@
       <c r="C136" t="n">
         <v>1</v>
       </c>
-      <c r="D136" t="inlineStr">
+      <c r="D136" t="inlineStr"/>
+      <c r="E136" t="inlineStr">
         <is>
           <t>LMOFIDA09TM</t>
         </is>
       </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F136" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -7439,17 +7648,18 @@
       <c r="C137" t="n">
         <v>1</v>
       </c>
-      <c r="D137" t="inlineStr">
+      <c r="D137" t="inlineStr"/>
+      <c r="E137" t="inlineStr">
         <is>
           <t>LMOFIDA31TM</t>
         </is>
       </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F137" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -7469,17 +7679,18 @@
       <c r="C138" t="n">
         <v>1</v>
       </c>
-      <c r="D138" t="inlineStr">
+      <c r="D138" t="inlineStr"/>
+      <c r="E138" t="inlineStr">
         <is>
           <t>MARMICA13T2XL</t>
         </is>
       </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F138" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -7499,17 +7710,18 @@
       <c r="C139" t="n">
         <v>1</v>
       </c>
-      <c r="D139" t="inlineStr">
+      <c r="D139" t="inlineStr"/>
+      <c r="E139" t="inlineStr">
         <is>
           <t>MARMICA16T2XL</t>
         </is>
       </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F139" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -7529,17 +7741,18 @@
       <c r="C140" t="n">
         <v>1</v>
       </c>
-      <c r="D140" t="inlineStr">
+      <c r="D140" t="inlineStr"/>
+      <c r="E140" t="inlineStr">
         <is>
           <t>MARMIDA01TS</t>
         </is>
       </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F140" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -7559,17 +7772,18 @@
       <c r="C141" t="n">
         <v>1</v>
       </c>
-      <c r="D141" t="inlineStr">
+      <c r="D141" t="inlineStr"/>
+      <c r="E141" t="inlineStr">
         <is>
           <t>MARMIDA11TXL</t>
         </is>
       </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F141" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -7589,17 +7803,18 @@
       <c r="C142" t="n">
         <v>1</v>
       </c>
-      <c r="D142" t="inlineStr">
+      <c r="D142" t="inlineStr"/>
+      <c r="E142" t="inlineStr">
         <is>
           <t>MARMIDA12TM</t>
         </is>
       </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F142" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -7619,17 +7834,18 @@
       <c r="C143" t="n">
         <v>1</v>
       </c>
-      <c r="D143" t="inlineStr">
+      <c r="D143" t="inlineStr"/>
+      <c r="E143" t="inlineStr">
         <is>
           <t>MARMIDA16TXL</t>
         </is>
       </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F143" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -7649,17 +7865,18 @@
       <c r="C144" t="n">
         <v>1</v>
       </c>
-      <c r="D144" t="inlineStr">
+      <c r="D144" t="inlineStr"/>
+      <c r="E144" t="inlineStr">
         <is>
           <t>MARMIKI13T10</t>
         </is>
       </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F144" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -7679,17 +7896,18 @@
       <c r="C145" t="n">
         <v>1</v>
       </c>
-      <c r="D145" t="inlineStr">
+      <c r="D145" t="inlineStr"/>
+      <c r="E145" t="inlineStr">
         <is>
           <t>MARMIKI13T8</t>
         </is>
       </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F145" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -7709,17 +7927,18 @@
       <c r="C146" t="n">
         <v>1</v>
       </c>
-      <c r="D146" t="inlineStr">
+      <c r="D146" t="inlineStr"/>
+      <c r="E146" t="inlineStr">
         <is>
           <t>MARMIKI16T4</t>
         </is>
       </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F146" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -7739,17 +7958,18 @@
       <c r="C147" t="n">
         <v>1</v>
       </c>
-      <c r="D147" t="inlineStr">
+      <c r="D147" t="inlineStr"/>
+      <c r="E147" t="inlineStr">
         <is>
           <t>MARMIKI34T14</t>
         </is>
       </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F147" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -7769,17 +7989,18 @@
       <c r="C148" t="n">
         <v>1</v>
       </c>
-      <c r="D148" t="inlineStr">
+      <c r="D148" t="inlineStr"/>
+      <c r="E148" t="inlineStr">
         <is>
           <t>MARMIKI34T8</t>
         </is>
       </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F148" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -7799,17 +8020,18 @@
       <c r="C149" t="n">
         <v>1</v>
       </c>
-      <c r="D149" t="inlineStr">
+      <c r="D149" t="inlineStr"/>
+      <c r="E149" t="inlineStr">
         <is>
           <t>MAYFNDA10TS</t>
         </is>
       </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F149" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -7829,17 +8051,18 @@
       <c r="C150" t="n">
         <v>1</v>
       </c>
-      <c r="D150" t="inlineStr">
+      <c r="D150" t="inlineStr"/>
+      <c r="E150" t="inlineStr">
         <is>
           <t>MAYFNDA10TXS</t>
         </is>
       </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F150" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -7859,17 +8082,18 @@
       <c r="C151" t="n">
         <v>1</v>
       </c>
-      <c r="D151" t="inlineStr">
+      <c r="D151" t="inlineStr"/>
+      <c r="E151" t="inlineStr">
         <is>
           <t>MAYFNDA13TM</t>
         </is>
       </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F151" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -7889,17 +8113,18 @@
       <c r="C152" t="n">
         <v>1</v>
       </c>
-      <c r="D152" t="inlineStr">
+      <c r="D152" t="inlineStr"/>
+      <c r="E152" t="inlineStr">
         <is>
           <t>MAYFNDA16TXS</t>
         </is>
       </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F152" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -7919,17 +8144,18 @@
       <c r="C153" t="n">
         <v>1</v>
       </c>
-      <c r="D153" t="inlineStr">
+      <c r="D153" t="inlineStr"/>
+      <c r="E153" t="inlineStr">
         <is>
           <t>MAYFNDA24TM</t>
         </is>
       </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F153" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -7949,17 +8175,18 @@
       <c r="C154" t="n">
         <v>1</v>
       </c>
-      <c r="D154" t="inlineStr">
+      <c r="D154" t="inlineStr"/>
+      <c r="E154" t="inlineStr">
         <is>
           <t>MAYFNDA24TS</t>
         </is>
       </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F154" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -7979,17 +8206,18 @@
       <c r="C155" t="n">
         <v>1</v>
       </c>
-      <c r="D155" t="inlineStr">
+      <c r="D155" t="inlineStr"/>
+      <c r="E155" t="inlineStr">
         <is>
           <t>MIKFNDA13TL</t>
         </is>
       </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F155" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -8009,17 +8237,18 @@
       <c r="C156" t="n">
         <v>1</v>
       </c>
-      <c r="D156" t="inlineStr">
+      <c r="D156" t="inlineStr"/>
+      <c r="E156" t="inlineStr">
         <is>
           <t>MIKFNDA13TS</t>
         </is>
       </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F156" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -8039,17 +8268,18 @@
       <c r="C157" t="n">
         <v>1</v>
       </c>
-      <c r="D157" t="inlineStr">
+      <c r="D157" t="inlineStr"/>
+      <c r="E157" t="inlineStr">
         <is>
           <t>MIKFNDA24TL</t>
         </is>
       </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F157" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -8069,17 +8299,18 @@
       <c r="C158" t="n">
         <v>1</v>
       </c>
-      <c r="D158" t="inlineStr">
+      <c r="D158" t="inlineStr"/>
+      <c r="E158" t="inlineStr">
         <is>
           <t>MIKFNDA24TXL</t>
         </is>
       </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F158" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -8099,17 +8330,18 @@
       <c r="C159" t="n">
         <v>1</v>
       </c>
-      <c r="D159" t="inlineStr">
+      <c r="D159" t="inlineStr"/>
+      <c r="E159" t="inlineStr">
         <is>
           <t>NAHFNCA24TS</t>
         </is>
       </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F159" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -8129,17 +8361,18 @@
       <c r="C160" t="n">
         <v>1</v>
       </c>
-      <c r="D160" t="inlineStr">
+      <c r="D160" t="inlineStr"/>
+      <c r="E160" t="inlineStr">
         <is>
           <t>RIOMICA70TS</t>
         </is>
       </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F160" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -8159,17 +8392,18 @@
       <c r="C161" t="n">
         <v>1</v>
       </c>
-      <c r="D161" t="inlineStr">
+      <c r="D161" t="inlineStr"/>
+      <c r="E161" t="inlineStr">
         <is>
           <t>RIOMIDA11TM</t>
         </is>
       </c>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F161" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -8189,17 +8423,18 @@
       <c r="C162" t="n">
         <v>1</v>
       </c>
-      <c r="D162" t="inlineStr">
+      <c r="D162" t="inlineStr"/>
+      <c r="E162" t="inlineStr">
         <is>
           <t>RIOMIDA11TS</t>
         </is>
       </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F162" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -8219,17 +8454,18 @@
       <c r="C163" t="n">
         <v>1</v>
       </c>
-      <c r="D163" t="inlineStr">
+      <c r="D163" t="inlineStr"/>
+      <c r="E163" t="inlineStr">
         <is>
           <t>RIOMIDA50TXL</t>
         </is>
       </c>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F163" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -8249,17 +8485,18 @@
       <c r="C164" t="n">
         <v>1</v>
       </c>
-      <c r="D164" t="inlineStr">
+      <c r="D164" t="inlineStr"/>
+      <c r="E164" t="inlineStr">
         <is>
           <t>RIOMIDA70TS</t>
         </is>
       </c>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F164" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -8279,17 +8516,18 @@
       <c r="C165" t="n">
         <v>1</v>
       </c>
-      <c r="D165" t="inlineStr">
+      <c r="D165" t="inlineStr"/>
+      <c r="E165" t="inlineStr">
         <is>
           <t>RIOMIKI04T12</t>
         </is>
       </c>
-      <c r="E165" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F165" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -8309,17 +8547,18 @@
       <c r="C166" t="n">
         <v>1</v>
       </c>
-      <c r="D166" t="inlineStr">
+      <c r="D166" t="inlineStr"/>
+      <c r="E166" t="inlineStr">
         <is>
           <t>RIOMIKI04T2</t>
         </is>
       </c>
-      <c r="E166" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F166" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -8339,17 +8578,18 @@
       <c r="C167" t="n">
         <v>1</v>
       </c>
-      <c r="D167" t="inlineStr">
+      <c r="D167" t="inlineStr"/>
+      <c r="E167" t="inlineStr">
         <is>
           <t>RIOMIKI13T2</t>
         </is>
       </c>
-      <c r="E167" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F167" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -8369,17 +8609,18 @@
       <c r="C168" t="n">
         <v>1</v>
       </c>
-      <c r="D168" t="inlineStr">
+      <c r="D168" t="inlineStr"/>
+      <c r="E168" t="inlineStr">
         <is>
           <t>RIOMIKI50T2</t>
         </is>
       </c>
-      <c r="E168" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F168" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -8399,17 +8640,18 @@
       <c r="C169" t="n">
         <v>1</v>
       </c>
-      <c r="D169" t="inlineStr">
+      <c r="D169" t="inlineStr"/>
+      <c r="E169" t="inlineStr">
         <is>
           <t>RUNTBMBFCA206TL</t>
         </is>
       </c>
-      <c r="E169" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F169" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -8429,17 +8671,18 @@
       <c r="C170" t="n">
         <v>1</v>
       </c>
-      <c r="D170" t="inlineStr">
+      <c r="D170" t="inlineStr"/>
+      <c r="E170" t="inlineStr">
         <is>
           <t>RUNTBMBFCA206TM</t>
         </is>
       </c>
-      <c r="E170" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F170" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -8459,17 +8702,18 @@
       <c r="C171" t="n">
         <v>1</v>
       </c>
-      <c r="D171" t="inlineStr">
+      <c r="D171" t="inlineStr"/>
+      <c r="E171" t="inlineStr">
         <is>
           <t>SARSPDA16TS</t>
         </is>
       </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F171" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -8489,17 +8733,18 @@
       <c r="C172" t="n">
         <v>1</v>
       </c>
-      <c r="D172" t="inlineStr">
+      <c r="D172" t="inlineStr"/>
+      <c r="E172" t="inlineStr">
         <is>
           <t>SARSPDA43TL</t>
         </is>
       </c>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F172" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -8519,17 +8764,18 @@
       <c r="C173" t="n">
         <v>1</v>
       </c>
-      <c r="D173" t="inlineStr">
+      <c r="D173" t="inlineStr"/>
+      <c r="E173" t="inlineStr">
         <is>
           <t>SARSPDA70TM</t>
         </is>
       </c>
-      <c r="E173" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F173" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -8549,17 +8795,18 @@
       <c r="C174" t="n">
         <v>1</v>
       </c>
-      <c r="D174" t="inlineStr">
+      <c r="D174" t="inlineStr"/>
+      <c r="E174" t="inlineStr">
         <is>
           <t>SARSPKI09T6</t>
         </is>
       </c>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F174" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -8579,17 +8826,18 @@
       <c r="C175" t="n">
         <v>1</v>
       </c>
-      <c r="D175" t="inlineStr">
+      <c r="D175" t="inlineStr"/>
+      <c r="E175" t="inlineStr">
         <is>
           <t>SARSPKI16T10</t>
         </is>
       </c>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F175" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -8609,17 +8857,18 @@
       <c r="C176" t="n">
         <v>1</v>
       </c>
-      <c r="D176" t="inlineStr">
+      <c r="D176" t="inlineStr"/>
+      <c r="E176" t="inlineStr">
         <is>
           <t>SHONRCA16TL</t>
         </is>
       </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F176" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -8639,17 +8888,18 @@
       <c r="C177" t="n">
         <v>1</v>
       </c>
-      <c r="D177" t="inlineStr">
+      <c r="D177" t="inlineStr"/>
+      <c r="E177" t="inlineStr">
         <is>
           <t>SHONRKI16T8</t>
         </is>
       </c>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F177" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -8669,17 +8919,18 @@
       <c r="C178" t="n">
         <v>1</v>
       </c>
-      <c r="D178" t="inlineStr">
+      <c r="D178" t="inlineStr"/>
+      <c r="E178" t="inlineStr">
         <is>
           <t>SHONTCA30TS</t>
         </is>
       </c>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F178" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -8699,17 +8950,18 @@
       <c r="C179" t="n">
         <v>1</v>
       </c>
-      <c r="D179" t="inlineStr">
+      <c r="D179" t="inlineStr"/>
+      <c r="E179" t="inlineStr">
         <is>
           <t>SHONTDA12TL</t>
         </is>
       </c>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F179" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -8729,17 +8981,18 @@
       <c r="C180" t="n">
         <v>1</v>
       </c>
-      <c r="D180" t="inlineStr">
+      <c r="D180" t="inlineStr"/>
+      <c r="E180" t="inlineStr">
         <is>
           <t>SHONTDA30TS</t>
         </is>
       </c>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F180" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -8759,17 +9012,18 @@
       <c r="C181" t="n">
         <v>1</v>
       </c>
-      <c r="D181" t="inlineStr">
+      <c r="D181" t="inlineStr"/>
+      <c r="E181" t="inlineStr">
         <is>
           <t>SHONTDA33TL</t>
         </is>
       </c>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F181" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -8789,17 +9043,18 @@
       <c r="C182" t="n">
         <v>1</v>
       </c>
-      <c r="D182" t="inlineStr">
+      <c r="D182" t="inlineStr"/>
+      <c r="E182" t="inlineStr">
         <is>
           <t>SHONTDA33TS</t>
         </is>
       </c>
-      <c r="E182" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F182" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -8819,17 +9074,18 @@
       <c r="C183" t="n">
         <v>1</v>
       </c>
-      <c r="D183" t="inlineStr">
+      <c r="D183" t="inlineStr"/>
+      <c r="E183" t="inlineStr">
         <is>
           <t>SHOSUCA153TXL</t>
         </is>
       </c>
-      <c r="E183" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F183" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -8849,17 +9105,18 @@
       <c r="C184" t="n">
         <v>1</v>
       </c>
-      <c r="D184" t="inlineStr">
+      <c r="D184" t="inlineStr"/>
+      <c r="E184" t="inlineStr">
         <is>
           <t>SHOSUCA156TM</t>
         </is>
       </c>
-      <c r="E184" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F184" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -8879,17 +9136,18 @@
       <c r="C185" t="n">
         <v>1</v>
       </c>
-      <c r="D185" t="inlineStr">
+      <c r="D185" t="inlineStr"/>
+      <c r="E185" t="inlineStr">
         <is>
           <t>SHOSUCA156TXL</t>
         </is>
       </c>
-      <c r="E185" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F185" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -8909,17 +9167,18 @@
       <c r="C186" t="n">
         <v>1</v>
       </c>
-      <c r="D186" t="inlineStr">
+      <c r="D186" t="inlineStr"/>
+      <c r="E186" t="inlineStr">
         <is>
           <t>SHOSUKI153T10</t>
         </is>
       </c>
-      <c r="E186" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F186" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -8939,17 +9198,18 @@
       <c r="C187" t="n">
         <v>1</v>
       </c>
-      <c r="D187" t="inlineStr">
+      <c r="D187" t="inlineStr"/>
+      <c r="E187" t="inlineStr">
         <is>
           <t>SHOSUKI153T6</t>
         </is>
       </c>
-      <c r="E187" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F187" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -8969,17 +9229,18 @@
       <c r="C188" t="n">
         <v>1</v>
       </c>
-      <c r="D188" t="inlineStr">
+      <c r="D188" t="inlineStr"/>
+      <c r="E188" t="inlineStr">
         <is>
           <t>SHOSUKI156T4</t>
         </is>
       </c>
-      <c r="E188" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F188" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -8999,17 +9260,18 @@
       <c r="C189" t="n">
         <v>1</v>
       </c>
-      <c r="D189" t="inlineStr">
+      <c r="D189" t="inlineStr"/>
+      <c r="E189" t="inlineStr">
         <is>
           <t>SHOSUKI156T6</t>
         </is>
       </c>
-      <c r="E189" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F189" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -9029,17 +9291,18 @@
       <c r="C190" t="n">
         <v>1</v>
       </c>
-      <c r="D190" t="inlineStr">
+      <c r="D190" t="inlineStr"/>
+      <c r="E190" t="inlineStr">
         <is>
           <t>SHUNTDA31TS</t>
         </is>
       </c>
-      <c r="E190" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F190" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -9059,17 +9322,18 @@
       <c r="C191" t="n">
         <v>1</v>
       </c>
-      <c r="D191" t="inlineStr">
+      <c r="D191" t="inlineStr"/>
+      <c r="E191" t="inlineStr">
         <is>
           <t>TMOFIDA31TL</t>
         </is>
       </c>
-      <c r="E191" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F191" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -9089,17 +9353,18 @@
       <c r="C192" t="n">
         <v>1</v>
       </c>
-      <c r="D192" t="inlineStr">
+      <c r="D192" t="inlineStr"/>
+      <c r="E192" t="inlineStr">
         <is>
           <t>TMOFIDA31TXS</t>
         </is>
       </c>
-      <c r="E192" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F192" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -9119,17 +9384,18 @@
       <c r="C193" t="n">
         <v>1</v>
       </c>
-      <c r="D193" t="inlineStr">
+      <c r="D193" t="inlineStr"/>
+      <c r="E193" t="inlineStr">
         <is>
           <t>VIVMIDA13TL</t>
         </is>
       </c>
-      <c r="E193" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F193" t="inlineStr">
+        <is>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -9149,19 +9415,666 @@
       <c r="C194" t="n">
         <v>1</v>
       </c>
-      <c r="D194" t="inlineStr">
+      <c r="D194" t="inlineStr"/>
+      <c r="E194" t="inlineStr">
         <is>
           <t>ZOEMIKI43T10</t>
         </is>
       </c>
-      <c r="E194" t="inlineStr">
-        <is>
-          <t>global:MANUFACTURADO</t>
-        </is>
-      </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>global:MANUFACTURADO</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>SKU</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>PRODUCTO</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>CANT</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>PRODUCTO_ODOO</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>SKU_CATALOGO</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>FUENTE</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>ESTADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>SSR2VIU43TL</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>R2 SPORT 5"</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>43</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>R2 SPORT  5" (Negro, L)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>SSR2VIU43TL</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>quants:Quants__stock.quant___1__5059.xlsx</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>ok_quants_odoo</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>SRR2VIU13TS</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>R2 RUNNING 3,5"</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>41</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>R2 RUNNING 3,5" (Azul Rey, S)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>SRR2VIU13TS</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>quants:Quants__stock.quant___2__3ab0.xlsx</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>ok_quants_odoo</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>SSR2VIU66TXL</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>R2 SPORT 5"</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>40</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>R2 SPORT  5" (Verde Militar, XL)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>SSR2VIU66TXL</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>quants:Quants__stock.quant___1__5059.xlsx</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>ok_quants_odoo</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SSR2VIU66TL</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>R2 SPORT 5"</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>35</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>R2 SPORT  5" (Verde Militar, L)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>SSR2VIU66TL</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>quants:Quants__stock.quant___1__5059.xlsx</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>ok_quants_odoo</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SSR2VIU43TS</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>R2 SPORT 5"</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>33</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>R2 SPORT  5" (Negro, S)</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>SSR2VIU43TS</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>quants:Quants__stock.quant___1__5059.xlsx</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>ok_quants_odoo</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>SSR2VIU70TM</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>R2 SPORT 5"</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>33</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>R2 SPORT  5" (Vinotinto, M)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>SSR2VIU70TM</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>quants:Quants__stock.quant___1__5059.xlsx</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>ok_quants_odoo</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>SSR2VIU66TM</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>R2 SPORT 5"</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>22</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>R2 SPORT  5" (Verde Militar, M)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>SSR2VIU66TM</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>quants:Quants__stock.quant___1__5059.xlsx</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>ok_quants_odoo</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>SRR2VIU43TS</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>R2 RUNNING 3,5"</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>21</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>R2 RUNNING 3,5" (Negro, S)</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>SRR2VIU43TS</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>ok_r2_inferred</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>ok_r2_inferred</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>SRR2VIU123TS</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>R2 RUNNING 3,5"</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>20</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>R2 RUNNING 3,5" (Azul Marino, S)</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>SRR2VIU123TS</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>ok_r2_inferred</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>ok_r2_inferred</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>SSR2VIU43TXL</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>R2 SPORT 5"</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>17</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>R2 SPORT  5" (Negro, XL)</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>SSR2VIU43TXL</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>quants:Quants__stock.quant___1__5059.xlsx</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>ok_quants_odoo</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>SRR2VIU123TM</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>R2 RUNNING 3,5"</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>13</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>R2 RUNNING 3,5" (Azul Marino, M)</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>SRR2VIU123TM</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>ok_r2_inferred</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>ok_r2_inferred</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>SRR2VIU123TL</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>R2 RUNNING 3,5"</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>8</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>R2 RUNNING 3,5" (Azul Marino, L)</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>SRR2VIU123TL</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>ok_r2_inferred</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>ok_r2_inferred</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>SSR2VIU43TM</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>R2 SPORT 5"</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>7</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>R2 SPORT  5" (Negro, M)</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>SSR2VIU43TM</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>quants:Quants__stock.quant___1__5059.xlsx</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>ok_quants_odoo</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>SRR2VIU123TXS</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>R2 RUNNING 3,5"</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>R2 RUNNING 3,5" (Azul Marino, XS)</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>SRR2VIU123TXS</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>ok_r2_inferred</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>ok_r2_inferred</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>SRR2VIU43TL</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>R2 RUNNING 3,5"</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>2</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>R2 RUNNING 3,5" (Negro, L)</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>SRR2VIU43TL</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>ok_r2_inferred</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>ok_r2_inferred</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>SRR2VIU43TM</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>R2 RUNNING 3,5"</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>R2 RUNNING 3,5" (Negro, M)</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>SRR2VIU43TM</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>ok_r2_inferred</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>ok_r2_inferred</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>SRR2VIU43TXS</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>R2 RUNNING 3,5"</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>R2 RUNNING 3,5" (Negro, XS)</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>SRR2VIU43TXS</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>ok_r2_inferred</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>ok_r2_inferred</t>
         </is>
       </c>
     </row>

--- a/output/SKU_ENTRADA_ALMACEN_completado.xlsx
+++ b/output/SKU_ENTRADA_ALMACEN_completado.xlsx
@@ -1628,7 +1628,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>MILA</t>
+          <t>MOTION LOOP MAFE DAMA</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -4055,12 +4055,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>ok_r2_inferred</t>
+          <t>quants:Quants__stock.quant___3__7680.xlsx</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>ok_r2_inferred</t>
+          <t>ok_quants_odoo</t>
         </is>
       </c>
     </row>
@@ -4173,7 +4173,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>R2 RUNNING 3,5" (Azul Marino, S)</t>
+          <t>R2 RUNNING 3,5" (Verde Manzana, S)</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>ok_r2_inferred</t>
+          <t>quants:Quants__stock.quant___3__7680.xlsx</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>ok_r2_inferred</t>
+          <t>ok_quants_odoo</t>
         </is>
       </c>
     </row>
@@ -4553,7 +4553,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>R2 RUNNING 3,5" (Azul Marino, M)</t>
+          <t>R2 RUNNING 3,5" (Verde Manzana, M)</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -4563,12 +4563,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>ok_r2_inferred</t>
+          <t>quants:Quants__stock.quant___3__7680.xlsx</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>ok_r2_inferred</t>
+          <t>ok_quants_odoo</t>
         </is>
       </c>
     </row>
@@ -5146,7 +5146,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>R2 RUNNING 3,5" (Azul Marino, L)</t>
+          <t>R2 RUNNING 3,5" (Verde Manzana, L)</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -5156,12 +5156,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>ok_r2_inferred</t>
+          <t>quants:Quants__stock.quant___3__7680.xlsx</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>ok_r2_inferred</t>
+          <t>ok_quants_odoo</t>
         </is>
       </c>
     </row>
@@ -5890,26 +5890,30 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>MILA</t>
+          <t>MOTION LOOP MAFE DAMA</t>
         </is>
       </c>
       <c r="C81" t="n">
         <v>3</v>
       </c>
-      <c r="D81" t="inlineStr"/>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>MOTION LOOP MAFE DAMA (Verde Militar, S)</t>
+        </is>
+      </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>MILMIDA66TS</t>
+          <t>MLMMJDA66TS</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>ok_catalog:alias_mila; global:MANUFACTURADO</t>
+          <t>odoo:known_label</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>ok_catalog:alias_mila</t>
+          <t>ok_odoo_known</t>
         </is>
       </c>
     </row>
@@ -6704,7 +6708,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>R2 RUNNING 3,5" (Azul Marino, XS)</t>
+          <t>R2 RUNNING 3,5" (Verde Manzana, XS)</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -6714,12 +6718,12 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>ok_r2_inferred</t>
+          <t>quants:Quants__stock.quant___3__7680.xlsx</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>ok_r2_inferred</t>
+          <t>ok_quants_odoo</t>
         </is>
       </c>
     </row>
@@ -9754,12 +9758,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ok_r2_inferred</t>
+          <t>quants:Quants__stock.quant___3__7680.xlsx</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>ok_r2_inferred</t>
+          <t>ok_quants_odoo</t>
         </is>
       </c>
     </row>
@@ -9779,7 +9783,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>R2 RUNNING 3,5" (Azul Marino, S)</t>
+          <t>R2 RUNNING 3,5" (Verde Manzana, S)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -9789,12 +9793,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ok_r2_inferred</t>
+          <t>quants:Quants__stock.quant___3__7680.xlsx</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>ok_r2_inferred</t>
+          <t>ok_quants_odoo</t>
         </is>
       </c>
     </row>
@@ -9849,7 +9853,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>R2 RUNNING 3,5" (Azul Marino, M)</t>
+          <t>R2 RUNNING 3,5" (Verde Manzana, M)</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -9859,12 +9863,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ok_r2_inferred</t>
+          <t>quants:Quants__stock.quant___3__7680.xlsx</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>ok_r2_inferred</t>
+          <t>ok_quants_odoo</t>
         </is>
       </c>
     </row>
@@ -9884,7 +9888,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>R2 RUNNING 3,5" (Azul Marino, L)</t>
+          <t>R2 RUNNING 3,5" (Verde Manzana, L)</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -9894,12 +9898,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ok_r2_inferred</t>
+          <t>quants:Quants__stock.quant___3__7680.xlsx</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>ok_r2_inferred</t>
+          <t>ok_quants_odoo</t>
         </is>
       </c>
     </row>
@@ -9954,7 +9958,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>R2 RUNNING 3,5" (Azul Marino, XS)</t>
+          <t>R2 RUNNING 3,5" (Verde Manzana, XS)</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -9964,12 +9968,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ok_r2_inferred</t>
+          <t>quants:Quants__stock.quant___3__7680.xlsx</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>ok_r2_inferred</t>
+          <t>ok_quants_odoo</t>
         </is>
       </c>
     </row>

--- a/output/SKU_ENTRADA_ALMACEN_completado.xlsx
+++ b/output/SKU_ENTRADA_ALMACEN_completado.xlsx
@@ -6753,12 +6753,12 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>ok_r2_inferred</t>
+          <t>quants:Quants__stock.quant___4__e718.xlsx</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>ok_r2_inferred</t>
+          <t>ok_quants_odoo</t>
         </is>
       </c>
     </row>
@@ -6788,12 +6788,12 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>ok_r2_inferred</t>
+          <t>quants:Quants__stock.quant___4__e718.xlsx</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>ok_r2_inferred</t>
+          <t>ok_quants_odoo</t>
         </is>
       </c>
     </row>
@@ -6823,12 +6823,12 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>ok_r2_inferred</t>
+          <t>quants:Quants__stock.quant___4__e718.xlsx</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>ok_r2_inferred</t>
+          <t>ok_quants_odoo</t>
         </is>
       </c>
     </row>
@@ -10003,12 +10003,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>ok_r2_inferred</t>
+          <t>quants:Quants__stock.quant___4__e718.xlsx</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>ok_r2_inferred</t>
+          <t>ok_quants_odoo</t>
         </is>
       </c>
     </row>
@@ -10038,12 +10038,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ok_r2_inferred</t>
+          <t>quants:Quants__stock.quant___4__e718.xlsx</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>ok_r2_inferred</t>
+          <t>ok_quants_odoo</t>
         </is>
       </c>
     </row>
@@ -10073,12 +10073,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>ok_r2_inferred</t>
+          <t>quants:Quants__stock.quant___4__e718.xlsx</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>ok_r2_inferred</t>
+          <t>ok_quants_odoo</t>
         </is>
       </c>
     </row>
